--- a/output/full_scan/batch_seq1_2026-09-16.xlsx
+++ b/output/full_scan/batch_seq1_2026-09-16.xlsx
@@ -5202,7 +5202,7 @@
         <v/>
       </c>
       <c r="D90" s="2" t="n">
-        <v>227.3818039198106</v>
+        <v>227.3818039198105</v>
       </c>
       <c r="E90" s="2" t="n">
         <v>99.90000000000001</v>
